--- a/SAEN PEÑA/Diciembre/SAENZ_EXPENSAS-Diciembre.xlsx
+++ b/SAEN PEÑA/Diciembre/SAENZ_EXPENSAS-Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SAEN PEÑA\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1720AB77-89A8-432F-9913-875C247661DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935D43CF-2203-4B5A-ABD7-B43BC2BBD7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="74">
   <si>
     <t>UF</t>
   </si>
@@ -244,7 +244,10 @@
     <t xml:space="preserve">Período DICIEMBRE </t>
   </si>
   <si>
-    <t>Federacion Patronal</t>
+    <t>Federacion Patronal - Sra. Nancy - Poliza 9200959</t>
+  </si>
+  <si>
+    <t>SAC - Diciembre - Sra. Nancy</t>
   </si>
 </sst>
 </file>
@@ -259,7 +262,7 @@
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,15 +370,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,12 +420,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="51">
     <border>
@@ -1069,7 +1059,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1284,6 +1274,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1344,9 +1335,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1715,22 +1703,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>20</v>
       </c>
@@ -1738,27 +1726,27 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
@@ -1770,7 +1758,7 @@
       </c>
       <c r="F7" s="98"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1778,24 +1766,24 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="101" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="97"/>
       <c r="C11" s="12"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="128" t="s">
+      <c r="E11" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="128"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="129"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="99"/>
       <c r="B12" s="99"/>
       <c r="C12" s="122"/>
@@ -1804,10 +1792,10 @@
         <v>48</v>
       </c>
       <c r="F12" s="121">
-        <v>270337.33266281988</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1555952.8226141399</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="97" t="s">
         <v>64</v>
       </c>
@@ -1823,17 +1811,17 @@
       </c>
       <c r="F13" s="50">
         <f>'prorrateo '!F11</f>
-        <v>1483168.0599513201</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>276680.51862200012</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="99" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="148">
+      <c r="C14" s="105">
         <v>32437.16</v>
       </c>
       <c r="D14" s="5"/>
@@ -1842,10 +1830,10 @@
       </c>
       <c r="F14" s="50">
         <f>-(C36)</f>
-        <v>-160707.91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-215715.42199999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="97" t="s">
         <v>21</v>
       </c>
@@ -1859,65 +1847,72 @@
       <c r="E15" s="49"/>
       <c r="F15" s="50"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="97"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="99" t="s">
+        <v>72</v>
+      </c>
       <c r="B16" s="97"/>
-      <c r="C16" s="71"/>
+      <c r="C16" s="71">
+        <v>8379</v>
+      </c>
       <c r="D16" s="5"/>
       <c r="E16" s="49"/>
       <c r="F16" s="50"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="149" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="149"/>
-      <c r="C17" s="150"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="50"/>
-    </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="102"/>
-      <c r="B18" s="103"/>
-      <c r="C18" s="126">
-        <f>SUM(C12:C17)</f>
-        <v>102422.27</v>
-      </c>
-      <c r="E18" s="51" t="s">
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="102"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="126">
+        <f>SUM(C12:C16)</f>
+        <v>110801.27</v>
+      </c>
+      <c r="E17" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="118">
+      <c r="F17" s="118">
         <f>SUM(F12:F15)</f>
-        <v>1592797.48261414</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="101" t="s">
+        <v>1616917.9192361401</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="97"/>
-      <c r="C19" s="127"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="20"/>
+    </row>
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="97" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="104" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="71">
+        <f xml:space="preserve"> 58285.64+58285.64*20%</f>
+        <v>69942.767999999996</v>
+      </c>
       <c r="D19" s="5"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="97" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="104" t="s">
-        <v>71</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B20" s="104"/>
       <c r="C20" s="71">
-        <f xml:space="preserve"> 56588+56588*3%</f>
-        <v>58285.64</v>
+        <f>C19/2</f>
+        <v>34971.383999999998</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="97" t="s">
         <v>68</v>
       </c>
@@ -1927,45 +1922,45 @@
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="97" t="s">
         <v>67</v>
       </c>
       <c r="B22" s="104"/>
       <c r="C22" s="105">
-        <f>400000-197552.6</f>
-        <v>202447.4</v>
+        <f>400000-215715.4</f>
+        <v>184284.6</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="102"/>
       <c r="B23" s="103"/>
       <c r="C23" s="119">
-        <f>SUM(C19:C22)</f>
-        <v>260733.03999999998</v>
+        <f>SUM(C18:C22)</f>
+        <v>289198.75199999998</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="47"/>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
         <v>14</v>
       </c>
       <c r="B24" s="41"/>
       <c r="C24" s="120">
-        <f>+C23+C18</f>
-        <v>363155.31</v>
+        <f>+C23+C17</f>
+        <v>400000.022</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60" t="s">
         <v>27</v>
       </c>
@@ -1974,18 +1969,18 @@
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="37"/>
       <c r="B27" s="28"/>
       <c r="C27" s="46"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
       <c r="B28" s="43"/>
       <c r="C28" s="45">
@@ -1993,7 +1988,7 @@
       </c>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="52"/>
       <c r="B29" s="53"/>
       <c r="C29" s="45">
@@ -2001,19 +1996,19 @@
       </c>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="69"/>
       <c r="B30" s="70"/>
       <c r="C30" s="72"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="69"/>
       <c r="B31" s="76"/>
       <c r="C31" s="77"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="69"/>
       <c r="B32" s="75"/>
       <c r="C32" s="72">
@@ -2021,7 +2016,7 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="54" t="s">
         <v>25</v>
       </c>
@@ -2031,91 +2026,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="123">
         <f>C24-C22</f>
-        <v>160707.91</v>
+        <v>215715.42199999999</v>
       </c>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C35" s="124">
         <f>+C24</f>
-        <v>363155.31</v>
+        <v>400000.022</v>
       </c>
       <c r="E35" s="100"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B36" s="55"/>
       <c r="C36" s="125">
         <f>C34</f>
-        <v>160707.91</v>
+        <v>215715.42199999999</v>
       </c>
       <c r="E36" s="16"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="16"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D45" s="16"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="19"/>
       <c r="B57" s="18"/>
       <c r="C57" s="20"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
@@ -2140,24 +2135,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="95" t="s">
         <v>60</v>
       </c>
@@ -2179,7 +2174,7 @@
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="63" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de DICIEMBRE</v>
@@ -2198,7 +2193,7 @@
       <c r="K2" s="67"/>
       <c r="L2" s="68"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2236,7 +2231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2266,7 +2261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2280,16 +2275,16 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>288499.71267936</v>
+        <v>373213.68854442623</v>
       </c>
       <c r="F5" s="71"/>
       <c r="G5" s="58">
         <f>E5-F5</f>
-        <v>288499.71267936</v>
+        <v>373213.68854442623</v>
       </c>
       <c r="H5" s="61">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>24233.975865066241</v>
+        <v>31349.949837731805</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
@@ -2304,10 +2299,10 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>373213.68854442623</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>465043.63838215801</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2321,19 +2316,16 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>299375.69391132006</v>
-      </c>
-      <c r="F6" s="71">
-        <f>E6</f>
-        <v>299375.69391132006</v>
-      </c>
+        <v>62760.000000000007</v>
+      </c>
+      <c r="F6" s="128"/>
       <c r="G6" s="58">
         <f t="shared" ref="G6:G8" si="0">E6-F6</f>
-        <v>0</v>
+        <v>62760.000000000007</v>
       </c>
       <c r="H6" s="61">
         <f t="shared" ref="H6:H10" si="1">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>0</v>
+        <v>5271.8400000000011</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
@@ -2348,10 +2340,10 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>62760.000000000007</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>130791.84000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2365,14 +2357,15 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>270650.92983600002</v>
-      </c>
-      <c r="F7" s="71">
-        <v>270651</v>
+        <v>63279.929836000025</v>
+      </c>
+      <c r="F7" s="128">
+        <f>E7</f>
+        <v>63279.929836000025</v>
       </c>
       <c r="G7" s="58">
         <f t="shared" si="0"/>
-        <v>-7.0163999975193292E-2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="61">
         <f t="shared" si="1"/>
@@ -2391,10 +2384,10 @@
       </c>
       <c r="L7" s="32">
         <f t="shared" ref="L7:L9" si="2">J7+K7+H7+G7</f>
-        <v>63279.929836000025</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>63280</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2408,11 +2401,11 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="E8" s="34">
-        <v>338741.36604000005</v>
-      </c>
-      <c r="F8" s="71">
-        <f t="shared" ref="F8" si="3">E8</f>
-        <v>338741.36604000005</v>
+        <v>79200</v>
+      </c>
+      <c r="F8" s="128">
+        <f>E8</f>
+        <v>79200</v>
       </c>
       <c r="G8" s="58">
         <f t="shared" si="0"/>
@@ -2438,7 +2431,7 @@
         <v>79200</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2452,14 +2445,15 @@
         <v>0.15920000000000001</v>
       </c>
       <c r="E9" s="34">
-        <v>272361.74481600005</v>
-      </c>
-      <c r="F9" s="71">
-        <v>272400</v>
+        <v>63641.744816000049</v>
+      </c>
+      <c r="F9" s="128">
+        <f>E9</f>
+        <v>63641.744816000049</v>
       </c>
       <c r="G9" s="58">
         <f>E9-F9</f>
-        <v>-38.255183999950532</v>
+        <v>0</v>
       </c>
       <c r="H9" s="61">
         <f t="shared" si="1"/>
@@ -2478,10 +2472,10 @@
       </c>
       <c r="L9" s="32">
         <f t="shared" si="2"/>
-        <v>63641.744816000049</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>63680</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2495,14 +2489,15 @@
         <v>0.17649999999999999</v>
       </c>
       <c r="E10" s="34">
-        <v>301958.84397000005</v>
-      </c>
-      <c r="F10" s="71">
-        <v>302000</v>
+        <v>70558.843970000045</v>
+      </c>
+      <c r="F10" s="128">
+        <f>E10</f>
+        <v>70558.843970000045</v>
       </c>
       <c r="G10" s="58">
         <f>E10-F10</f>
-        <v>-41.156029999954626</v>
+        <v>0</v>
       </c>
       <c r="H10" s="61">
         <f t="shared" si="1"/>
@@ -2521,10 +2516,10 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>70558.843970000045</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>70600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2535,56 +2530,56 @@
         <v>1</v>
       </c>
       <c r="E11" s="35">
-        <f t="shared" ref="E11" si="4">SUM(E5:E10)</f>
-        <v>1771588.2912526804</v>
+        <f t="shared" ref="E11" si="3">SUM(E5:E10)</f>
+        <v>712654.20716642635</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>1483168.0599513201</v>
+        <v>276680.51862200012</v>
       </c>
       <c r="G11" s="42">
         <f>SUM(G5:G10)</f>
-        <v>288420.23130136012</v>
+        <v>435973.68854442623</v>
       </c>
       <c r="H11" s="42">
-        <f t="shared" ref="H11:K11" si="5">SUM(H5:H10)</f>
-        <v>24233.975865066241</v>
+        <f t="shared" ref="H11:K11" si="4">SUM(H5:H10)</f>
+        <v>36621.789837731805</v>
       </c>
       <c r="I11" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J11" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400000</v>
       </c>
       <c r="K11" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L11" s="42">
         <f>SUM(L5:L10)</f>
-        <v>712654.20716642635</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="129"/>
-      <c r="B12" s="129"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="129"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="129"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>872595.47838215809</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="130"/>
+      <c r="B12" s="130"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="130"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2604,21 +2599,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="106" t="s">
         <v>69</v>
       </c>
@@ -2627,13 +2622,13 @@
       <c r="D1" s="108"/>
       <c r="E1" s="109"/>
       <c r="F1" s="108"/>
-      <c r="G1" s="130">
+      <c r="G1" s="131">
         <v>4500000</v>
       </c>
-      <c r="H1" s="130"/>
+      <c r="H1" s="131"/>
       <c r="I1" s="110"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2662,7 +2657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2683,7 +2678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -2715,7 +2710,7 @@
         <v>680400</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -2747,7 +2742,7 @@
         <v>706050</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>3</v>
       </c>
@@ -2779,7 +2774,7 @@
         <v>711900</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>4</v>
       </c>
@@ -2811,7 +2806,7 @@
         <v>891000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>5</v>
       </c>
@@ -2843,7 +2838,7 @@
         <v>716400</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>6</v>
       </c>
@@ -2875,7 +2870,7 @@
         <v>794250</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="113" t="s">
         <v>10</v>
       </c>
@@ -2906,21 +2901,21 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="129"/>
-      <c r="B11" s="129"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I12" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
@@ -2938,68 +2933,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="136" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="138"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="139"/>
       <c r="F1" s="78"/>
       <c r="G1" s="78"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="139" t="s">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="140" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="140"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="142">
+      <c r="B2" s="141"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="143">
         <v>565</v>
       </c>
-      <c r="E2" s="143"/>
+      <c r="E2" s="144"/>
       <c r="F2" s="79"/>
       <c r="G2" s="79"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="144" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="144" t="s">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="145" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="145" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="144" t="s">
+      <c r="C3" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="146" t="s">
+      <c r="D3" s="147" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="131" t="s">
+      <c r="E3" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="131" t="s">
+      <c r="F3" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="131" t="s">
+      <c r="G3" s="132" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="145"/>
-      <c r="B4" s="145"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="146"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="80">
         <v>1</v>
       </c>
@@ -3022,7 +3017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="80">
         <v>2</v>
       </c>
@@ -3045,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="80">
         <v>3</v>
       </c>
@@ -3068,7 +3063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="80">
         <v>4</v>
       </c>
@@ -3091,7 +3086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="80">
         <v>5</v>
       </c>
@@ -3114,7 +3109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="85">
         <v>6</v>
       </c>
@@ -3137,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="90" t="s">
         <v>10</v>
       </c>
@@ -3156,12 +3151,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="133"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="134"/>
-      <c r="D12" s="134"/>
-      <c r="E12" s="135"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="134"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="136"/>
       <c r="F12" s="78"/>
       <c r="G12" s="78"/>
     </row>
